--- a/survey_templates/038_music_and_play_knowledge_quiz--survey_templates.xlsx
+++ b/survey_templates/038_music_and_play_knowledge_quiz--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -730,7 +730,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C30"/>
+  <dimension ref="A1:C29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
@@ -1103,12 +1103,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>studio</t>
+          <t>community_center</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Studio</t>
+          <t>Community Center</t>
         </is>
       </c>
     </row>
@@ -1120,29 +1120,29 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>community_center</t>
+          <t>arena</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Community Center</t>
+          <t>Arena</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>event_organizers_choices</t>
+          <t>educators_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>arena</t>
+          <t>teacher</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Arena</t>
+          <t>Teacher</t>
         </is>
       </c>
     </row>
@@ -1154,12 +1154,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>teacher</t>
+          <t>professor</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Teacher</t>
+          <t>Professor</t>
         </is>
       </c>
     </row>
@@ -1171,12 +1171,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>professor</t>
+          <t>artist</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Professor</t>
+          <t>Artist</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>artist</t>
+          <t>educator</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Artist</t>
+          <t>Educator</t>
         </is>
       </c>
     </row>
@@ -1205,12 +1205,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>educator</t>
+          <t>director</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Educator</t>
+          <t>Director</t>
         </is>
       </c>
     </row>
@@ -1222,27 +1222,10 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>director</t>
+          <t>producer</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
-        <is>
-          <t>Director</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>educators_choices</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>producer</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
         <is>
           <t>Producer</t>
         </is>
